--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2021.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:16</t>
+    <t xml:space="preserve">2026-09-09 21:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2021.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:00</t>
+    <t xml:space="preserve">2026-09-17 13:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2021.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:47</t>
+    <t xml:space="preserve">2026-10-05 18:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -586,7 +586,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>813719.62</v>
+        <v>813719.63</v>
       </c>
     </row>
     <row r="15">
@@ -602,7 +602,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>871590.12</v>
+        <v>871590.13</v>
       </c>
     </row>
     <row r="17">
